--- a/practice_test/real_document/generated/PRJ-9201_tender_pack_r1/PRJ-9201-D45_r1_Final-document-manifest.xlsx
+++ b/practice_test/real_document/generated/PRJ-9201_tender_pack_r1/PRJ-9201-D45_r1_Final-document-manifest.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11c8ae20df7f18a886ad048ff027d0ade31b5fd0a78f5db38bfe04fecf099f98</t>
+          <t>7c6573ef4c50a913536d205fa9a5a3b52e8f6f43832c176bbabd9f7a37cba2ea</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2a02468db71d2f8643f08c7d023bcb2b57defec30271146bf99538e52646dcdd</t>
+          <t>f5a46decb10f84a75c12e5b8f62d4425d51b1c7cf50ac45343032103eb696fbf</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>79045e09221464067d1de812954aded0a629fdadab5bb929aae9f6798179118d</t>
+          <t>c6baff76a43bd5ed89ab694536678037df5be93db630f41a96889eb46a6bb07f</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>a84c244371d41701acca792106e6de2e14d708660989623b18421c1ce2ce8bc1</t>
+          <t>5d83f3a57fbf77efc6bdf44905be90a6caf4e6e96ed399abe8948ee45e06f374</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5ac9ce5881257c61d5c6c0f10eb668876421f3b171495eeb061cbc97a7d6167a</t>
+          <t>ea677a1021c493a737acab757163473dd7621df485aae7ce1696149b956f8b1e</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2d73bbb7436160a1a15495daefd97c442e11711500962cf8fba15c26fbae9b62</t>
+          <t>cdaba6f1abd078ce3e5a38c980cc071164c38084e3c529db2d3eb8b4c329a5cf</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2bf6147eb0831d0ee4d2e9303f1571a082297f80861cf16fd303e67dc98db930</t>
+          <t>bae6e527eac1a048c4b1f55e6f84c2cfc7b096f26eb7d7cd3eb6b04ca9cd9a48</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>287de1f51bbbfdceb7e62334214a066d79b0e7241f7749829711b3d20e4bf01c</t>
+          <t>75b7455a02129c56ec5fc787ff5136f25875ddf08b4494121f8c173e9ff9237b</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>7d3f942a9529b4d39286148ce7365e2dfeb25fc59332eeb1d5f41dff356a3fcd</t>
+          <t>fa8df0a1e1d0657baa975311ec0d64fe43a56b602c990bd45767fc6d5e906982</t>
         </is>
       </c>
     </row>
